--- a/DATA_INPUT/opal/ROI_Compositions_public.xlsx
+++ b/DATA_INPUT/opal/ROI_Compositions_public.xlsx
@@ -1,85 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Spoiler\SPOILER_Submission\DATA_INPUT\opal\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298C34C8-FEE0-4D34-B523-AF6F4FCFC341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="140" yWindow="0" windowWidth="18380" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">ROI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PanCK+/MUC5B+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PanCK+/MUC5B-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD66b+/MPO+/ARG-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD66b+/MPO+/ARG+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD66b+_Combined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non_PANCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUC5B_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD66b+_Prop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANCK_CD66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+  <si>
+    <t>ROI</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>PanCK+/MUC5B+</t>
+  </si>
+  <si>
+    <t>PanCK+/MUC5B-</t>
+  </si>
+  <si>
+    <t>CD66b+/MPO+/ARG-</t>
+  </si>
+  <si>
+    <t>CD66b+/MPO+/ARG+</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>CD66b+_Combined</t>
+  </si>
+  <si>
+    <t>PANCK</t>
+  </si>
+  <si>
+    <t>Non_PANCK</t>
+  </si>
+  <si>
+    <t>MUC5B_Prop</t>
+  </si>
+  <si>
+    <t>CD66b+_Prop</t>
+  </si>
+  <si>
+    <t>PANCK_CD66</t>
+  </si>
+  <si>
+    <t>Pt_14</t>
+  </si>
+  <si>
+    <t>Pt_05</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>Pt_13</t>
+  </si>
+  <si>
+    <t>Pt_04</t>
+  </si>
+  <si>
+    <t>Pt_02</t>
+  </si>
+  <si>
+    <t>ECLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -115,6 +122,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,11 +412,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,213 +457,213 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>31</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>135</v>
+      </c>
+      <c r="H2">
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <v>31</v>
+      </c>
+      <c r="J2">
+        <v>157</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0.14012738853503201</v>
+      </c>
+      <c r="M2">
+        <v>0.628571428571429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
+      <c r="D3">
+        <v>41</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>393</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>42</v>
+      </c>
+      <c r="J3">
+        <v>395</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="M3">
+        <v>6.4516129032258104E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G2" t="n">
-        <v>135</v>
-      </c>
-      <c r="H2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J2" t="n">
-        <v>157</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>212</v>
+      </c>
+      <c r="H4">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>48</v>
+      </c>
+      <c r="J4">
+        <v>231</v>
+      </c>
+      <c r="K4">
+        <v>0.875</v>
+      </c>
+      <c r="L4">
+        <v>8.3665338645418294E-2</v>
+      </c>
+      <c r="M4">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.140127388535032</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.628571428571429</v>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>173</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>51</v>
+      </c>
+      <c r="J5">
+        <v>176</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1.4598540145985399E-2</v>
+      </c>
+      <c r="M5">
+        <v>4.6875E-2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>41</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>393</v>
-      </c>
-      <c r="H3" t="n">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J3" t="n">
-        <v>395</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.0645161290322581</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>212</v>
-      </c>
-      <c r="H4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J4" t="n">
-        <v>231</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0836653386454183</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>173</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>51</v>
-      </c>
-      <c r="J5" t="n">
-        <v>176</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0145985401459854</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.046875</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>56</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>21</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>141</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>239</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>158</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>58</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>380</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.947368421052632</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.41578947368421</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.36206896551724</v>
+      <c r="K6">
+        <v>0.94736842105263197</v>
+      </c>
+      <c r="L6">
+        <v>0.41578947368420999</v>
+      </c>
+      <c r="M6">
+        <v>2.3620689655172402</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>